--- a/astro-site/public/dl/taco-shop-checklist-templates/03-taco-shop-food-safety-salsa-bar-allergens.xlsx
+++ b/astro-site/public/dl/taco-shop-checklist-templates/03-taco-shop-food-safety-salsa-bar-allergens.xlsx
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Keep baking tree nuts apart from the rest of the salsa bar</t>
+          <t>Keep tree nuts (almonds, pecans, walnuts) apart from the rest of the salsa bar</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Check the counter team can give allergen information on the 9 major allergens (UK: 14)</t>
+          <t>Check the counter team can give allergen info on all 9 major allergens: also shrimp and fish, and the egg, milk and soy in batters, crema and marinades (UK: 14)</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
